--- a/scenarios/07_karen_test_engineer/7.4_cold_stop_sweep/outputs/cold_stop_sweep_results.xlsx
+++ b/scenarios/07_karen_test_engineer/7.4_cold_stop_sweep/outputs/cold_stop_sweep_results.xlsx
@@ -533,22 +533,22 @@
         <v>0.02</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>16250</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>16250</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>127.47</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1363</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="6">
@@ -556,22 +556,22 @@
         <v>0.04</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>32500</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>32500</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>180.28</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1360.59</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="7">
@@ -579,22 +579,22 @@
         <v>0.06</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>48750</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>48750</v>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>220.79</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1358.19</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="8">
@@ -602,22 +602,22 @@
         <v>0.08</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>64999</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>64999</v>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>254.95</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1355.8</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +625,22 @@
         <v>0.1</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>81249</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>81249</v>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>285.04</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1353.42</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="10">
@@ -648,22 +648,22 @@
         <v>0.12</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>97499</v>
+        <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>97499</v>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>312.25</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1351.06</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="11">
@@ -671,22 +671,22 @@
         <v>0.14</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>113749</v>
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>113749</v>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>337.27</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1348.71</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="12">
@@ -694,22 +694,22 @@
         <v>0.16</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>129999</v>
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>129999</v>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>360.55</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1346.37</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="13">
@@ -717,22 +717,22 @@
         <v>0.18</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>146249</v>
+        <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>146249</v>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>382.42</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1344.05</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="14">
@@ -740,22 +740,22 @@
         <v>0.2</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>162499</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>162499</v>
+      <c r="D14" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>403.11</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1341.73</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="15">
@@ -763,22 +763,22 @@
         <v>0.22</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>178748</v>
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>178748</v>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>422.79</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1339.43</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="16">
@@ -786,22 +786,22 @@
         <v>0.24</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>194998</v>
+        <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>194998</v>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>441.59</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1337.14</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="17">
@@ -809,22 +809,22 @@
         <v>0.26</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>211248</v>
+        <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>211248</v>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>459.62</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1334.86</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="18">
@@ -832,22 +832,22 @@
         <v>0.28</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>227498</v>
+        <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="5" t="n">
-        <v>227498</v>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>476.97</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1332.59</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="19">
@@ -855,22 +855,22 @@
         <v>0.3</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>243748</v>
+        <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>243748</v>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>493.71</v>
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1330.34</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="20">
@@ -878,22 +878,22 @@
         <v>0.32</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>259998</v>
+        <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>259998</v>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>509.9</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1328.09</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="21">
@@ -901,22 +901,22 @@
         <v>0.34</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>276248</v>
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>276248</v>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>525.59</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1325.86</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="22">
@@ -924,22 +924,22 @@
         <v>0.36</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>292497</v>
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="5" t="n">
-        <v>292497</v>
+      <c r="D22" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>540.83</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1323.64</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="23">
@@ -947,22 +947,22 @@
         <v>0.38</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>308747</v>
+        <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>308747</v>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>555.65</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1321.43</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="24">
@@ -970,22 +970,22 @@
         <v>0.4</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>324997</v>
+        <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>324997</v>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>570.09</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1319.23</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="25">
@@ -993,22 +993,22 @@
         <v>0.42</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>341247</v>
+        <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>341247</v>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>584.16</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1317.04</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="26">
@@ -1016,22 +1016,22 @@
         <v>0.44</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>357497</v>
+        <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>357497</v>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>597.91</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1314.87</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="27">
@@ -1039,22 +1039,22 @@
         <v>0.46</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>373747</v>
+        <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>373747</v>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>611.35</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1312.7</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="28">
@@ -1062,22 +1062,22 @@
         <v>0.48</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>389997</v>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>389997</v>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>624.5</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1310.54</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="29">
@@ -1085,22 +1085,22 @@
         <v>0.5</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>406246</v>
+        <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>406246</v>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>637.37</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1308.4</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="30">
@@ -1108,22 +1108,22 @@
         <v>0.52</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>422496</v>
+        <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>422496</v>
+      <c r="D30" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1306.26</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="31">
@@ -1131,22 +1131,22 @@
         <v>0.54</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>438746</v>
+        <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>438746</v>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>662.38</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1304.14</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="32">
@@ -1154,22 +1154,22 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>454996</v>
+        <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="5" t="n">
-        <v>454996</v>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>674.53</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1302.02</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="33">
@@ -1177,22 +1177,22 @@
         <v>0.58</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>471246</v>
+        <v>0</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="5" t="n">
-        <v>471246</v>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>686.47</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1299.92</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="34">
@@ -1200,22 +1200,22 @@
         <v>0.6</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>487496</v>
+        <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="5" t="n">
-        <v>487496</v>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>698.21</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1297.83</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         <v>0.62</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>503746</v>
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>503746</v>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>709.75</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1295.74</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="36">
@@ -1246,22 +1246,22 @@
         <v>0.64</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>519995</v>
+        <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D36" s="5" t="n">
-        <v>519995</v>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>721.11</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1293.67</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="37">
@@ -1269,22 +1269,22 @@
         <v>0.66</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>536245</v>
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="5" t="n">
-        <v>536245</v>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>732.29</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1291.6</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="38">
@@ -1292,22 +1292,22 @@
         <v>0.68</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>552495</v>
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="5" t="n">
-        <v>552495</v>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>743.3</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>1289.55</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="39">
@@ -1315,22 +1315,22 @@
         <v>0.7</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>568745</v>
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="5" t="n">
-        <v>568745</v>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>754.15</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1287.51</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="40">
@@ -1338,22 +1338,22 @@
         <v>0.72</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>584995</v>
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="5" t="n">
-        <v>584995</v>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>764.85</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1285.47</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="41">
@@ -1361,22 +1361,22 @@
         <v>0.74</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>601245</v>
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="5" t="n">
-        <v>601245</v>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>775.4</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1283.45</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="42">
@@ -1384,22 +1384,22 @@
         <v>0.76</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>617495</v>
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="5" t="n">
-        <v>617495</v>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>785.8099999999999</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1281.43</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="43">
@@ -1407,22 +1407,22 @@
         <v>0.78</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>633744</v>
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="5" t="n">
-        <v>633744</v>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>796.08</v>
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1279.43</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="44">
@@ -1430,22 +1430,22 @@
         <v>0.8</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>649994</v>
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="5" t="n">
-        <v>649994</v>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>806.22</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>1277.43</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="45">
@@ -1453,22 +1453,22 @@
         <v>0.82</v>
       </c>
       <c r="B45" s="3" t="n">
-        <v>666244</v>
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>666244</v>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>816.24</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1275.44</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="46">
@@ -1476,22 +1476,22 @@
         <v>0.84</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>682494</v>
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="5" t="n">
-        <v>682494</v>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>826.13</v>
+        <v>0</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1273.46</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="47">
@@ -1499,22 +1499,22 @@
         <v>0.86</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>698744</v>
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="5" t="n">
-        <v>698744</v>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>835.91</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>1271.5</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="48">
@@ -1522,22 +1522,22 @@
         <v>0.88</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>714994</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>714994</v>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>845.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1269.54</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="49">
@@ -1545,22 +1545,22 @@
         <v>0.9</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>731244</v>
+        <v>0</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="5" t="n">
-        <v>731244</v>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>855.13</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>1267.58</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="50">
@@ -1568,22 +1568,22 @@
         <v>0.92</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>747493</v>
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>747493</v>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>864.58</v>
+        <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1265.64</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="51">
@@ -1591,22 +1591,22 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>763743</v>
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="5" t="n">
-        <v>763743</v>
+      <c r="D51" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>873.92</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1263.71</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="52">
@@ -1614,22 +1614,22 @@
         <v>0.96</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>779993</v>
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="5" t="n">
-        <v>779993</v>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>883.17</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1261.79</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="53">
@@ -1637,22 +1637,22 @@
         <v>0.98</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>796243</v>
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="5" t="n">
-        <v>796243</v>
+      <c r="D53" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>892.3200000000001</v>
+        <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1259.87</v>
+        <v>1365.42</v>
       </c>
     </row>
     <row r="54">
@@ -1660,22 +1660,22 @@
         <v>1</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>812493</v>
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="5" t="n">
-        <v>812493</v>
+      <c r="D54" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>901.38</v>
+        <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>1280.71</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1257.97</v>
+        <v>1365.42</v>
       </c>
     </row>
   </sheetData>
@@ -1745,8 +1745,10 @@
       <c r="C4" s="3" t="n">
         <v>35500</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0.0437</v>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1766,8 +1768,10 @@
       <c r="C5" s="3" t="n">
         <v>39500</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>0.0486</v>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1787,8 +1791,10 @@
       <c r="C6" s="3" t="n">
         <v>44000</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>0.0542</v>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -1808,8 +1814,10 @@
       <c r="C7" s="3" t="n">
         <v>47750</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>0.0588</v>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -1829,8 +1837,10 @@
       <c r="C8" s="3" t="n">
         <v>52000</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>0.064</v>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -1850,8 +1860,10 @@
       <c r="C9" s="3" t="n">
         <v>55750</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>0.06859999999999999</v>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -1870,7 +1882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1972,7 +1984,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>812493</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1996,127 +2008,187 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1258.0</t>
+          <t>1365.4</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEDT [mK]</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20.54</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Requirements</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NIIRS [—]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Max shuttered background [e⁻]</t>
+          <t>MTF at Nyquist [—]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>40000</t>
+          <t>0.3175</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Max η_cold to meet requirement [—]</t>
+          <t>Strehl ratio [—]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.0492</t>
+          <t>1.0000</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Well margin [dB]</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9.29</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Lab Results</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CS-NOM (0.0 mm offset)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>35500 e⁻ → η = 0.0437 [PASS]</t>
-        </is>
-      </c>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Requirements</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CS-OFF-05 (0.5 mm offset)</t>
+          <t>Max shuttered background [e⁻]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>39500 e⁻ → η = 0.0486 [PASS]</t>
+          <t>40000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CS-OFF-10 (1.0 mm offset)</t>
+          <t>Max η_cold to meet requirement [—]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>44000 e⁻ → η = 0.0542 [FAIL]</t>
+          <t>1.0000</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CS-OFF-15 (1.5 mm offset)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>47750 e⁻ → η = 0.0588 [FAIL]</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CS-OFF-20 (2.0 mm offset)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>52000 e⁻ → η = 0.0640 [FAIL]</t>
-        </is>
-      </c>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Lab Results</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>CS-NOM (0.0 mm offset)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>35500 e⁻ → η = N/A [PASS]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CS-OFF-05 (0.5 mm offset)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>39500 e⁻ → η = N/A [PASS]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CS-OFF-10 (1.0 mm offset)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>44000 e⁻ → η = N/A [FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CS-OFF-15 (1.5 mm offset)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>47750 e⁻ → η = N/A [FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CS-OFF-20 (2.0 mm offset)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>52000 e⁻ → η = N/A [FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>CS-OFF-25 (2.5 mm offset)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>55750 e⁻ → η = 0.0686 [FAIL]</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>55750 e⁻ → η = N/A [FAIL]</t>
         </is>
       </c>
     </row>
